--- a/data/Taller_DET_Agosto/Swap_8lhds/elmo_data.xlsx
+++ b/data/Taller_DET_Agosto/Swap_8lhds/elmo_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Taller_DET_Agosto\Swap_8lhds\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_infrastructure_NP\data\Taller_DET_Agosto\Swap_8lhds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD363D0-1B27-4C48-9D55-3702BAEFB543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD39DA27-5C11-4829-AEEA-E561CFECA9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="318">
   <si>
     <t>id</t>
   </si>
@@ -177,9 +177,6 @@
     <t>g/kWh</t>
   </si>
   <si>
-    <t>total_chargers</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -994,9 +991,6 @@
   </si>
   <si>
     <t>LH518B_8</t>
-  </si>
-  <si>
-    <t>electric</t>
   </si>
 </sst>
 </file>
@@ -1498,39 +1492,38 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AD10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AC10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" style="5" customWidth="1"/>
-    <col min="16" max="16" width="16.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18" style="6" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="20.85546875" style="6" customWidth="1"/>
-    <col min="24" max="24" width="18.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="20.88671875" style="6" customWidth="1"/>
+    <col min="24" max="24" width="18.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1538,7 +1531,7 @@
         <v>12</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D1" s="10" t="s">
         <v>13</v>
@@ -1553,7 +1546,7 @@
         <v>14</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I1" s="10" t="s">
         <v>15</v>
@@ -1595,34 +1588,31 @@
         <v>28</v>
       </c>
       <c r="V1" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="W1" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="W1" s="10" t="s">
-        <v>51</v>
       </c>
       <c r="X1" s="10" t="s">
         <v>20</v>
       </c>
       <c r="Y1" s="10" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="Z1" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA1" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB1" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC1" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD1" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1645,7 +1635,7 @@
         <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I2" t="s">
         <v>40</v>
@@ -1696,10 +1686,10 @@
         <v>30</v>
       </c>
       <c r="Y2" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="Z2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AA2" t="s">
         <v>33</v>
@@ -1708,13 +1698,10 @@
         <v>33</v>
       </c>
       <c r="AC2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1722,16 +1709,16 @@
         <v>36</v>
       </c>
       <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" t="s">
+        <v>308</v>
+      </c>
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" t="s">
         <v>67</v>
-      </c>
-      <c r="D3" t="s">
-        <v>309</v>
-      </c>
-      <c r="E3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" t="s">
-        <v>68</v>
       </c>
       <c r="G3">
         <v>18</v>
@@ -1788,42 +1775,39 @@
         <v>320</v>
       </c>
       <c r="Y3">
-        <v>4</v>
+        <v>482</v>
       </c>
       <c r="Z3">
-        <v>482</v>
+        <v>0.2</v>
       </c>
       <c r="AA3">
-        <v>0.2</v>
+        <v>0.95</v>
       </c>
       <c r="AB3">
         <v>0.95</v>
       </c>
       <c r="AC3">
-        <v>0.95</v>
-      </c>
-      <c r="AD3">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" t="s">
+        <v>308</v>
+      </c>
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" t="s">
         <v>67</v>
-      </c>
-      <c r="D4" t="s">
-        <v>309</v>
-      </c>
-      <c r="E4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" t="s">
-        <v>68</v>
       </c>
       <c r="G4">
         <v>18</v>
@@ -1880,42 +1864,39 @@
         <v>320</v>
       </c>
       <c r="Y4">
-        <v>4</v>
+        <v>482</v>
       </c>
       <c r="Z4">
-        <v>482</v>
+        <v>0.2</v>
       </c>
       <c r="AA4">
-        <v>0.2</v>
+        <v>0.95</v>
       </c>
       <c r="AB4">
         <v>0.95</v>
       </c>
       <c r="AC4">
-        <v>0.95</v>
-      </c>
-      <c r="AD4">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" t="s">
+        <v>308</v>
+      </c>
+      <c r="E5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" t="s">
         <v>67</v>
-      </c>
-      <c r="D5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" t="s">
-        <v>68</v>
       </c>
       <c r="G5">
         <v>18</v>
@@ -1972,42 +1953,39 @@
         <v>320</v>
       </c>
       <c r="Y5">
-        <v>4</v>
+        <v>482</v>
       </c>
       <c r="Z5">
-        <v>482</v>
+        <v>0.2</v>
       </c>
       <c r="AA5">
-        <v>0.2</v>
+        <v>0.95</v>
       </c>
       <c r="AB5">
         <v>0.95</v>
       </c>
       <c r="AC5">
-        <v>0.95</v>
-      </c>
-      <c r="AD5">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" t="s">
+        <v>308</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s">
         <v>67</v>
-      </c>
-      <c r="D6" t="s">
-        <v>309</v>
-      </c>
-      <c r="E6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" t="s">
-        <v>68</v>
       </c>
       <c r="G6">
         <v>18</v>
@@ -2064,42 +2042,39 @@
         <v>320</v>
       </c>
       <c r="Y6">
-        <v>4</v>
+        <v>482</v>
       </c>
       <c r="Z6">
-        <v>482</v>
+        <v>0.2</v>
       </c>
       <c r="AA6">
-        <v>0.2</v>
+        <v>0.95</v>
       </c>
       <c r="AB6">
         <v>0.95</v>
       </c>
       <c r="AC6">
-        <v>0.95</v>
-      </c>
-      <c r="AD6">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" t="s">
+        <v>308</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s">
         <v>67</v>
-      </c>
-      <c r="D7" t="s">
-        <v>309</v>
-      </c>
-      <c r="E7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" t="s">
-        <v>68</v>
       </c>
       <c r="G7">
         <v>18</v>
@@ -2156,42 +2131,39 @@
         <v>320</v>
       </c>
       <c r="Y7">
-        <v>4</v>
+        <v>482</v>
       </c>
       <c r="Z7">
-        <v>482</v>
+        <v>0.2</v>
       </c>
       <c r="AA7">
-        <v>0.2</v>
+        <v>0.95</v>
       </c>
       <c r="AB7">
         <v>0.95</v>
       </c>
       <c r="AC7">
-        <v>0.95</v>
-      </c>
-      <c r="AD7">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" t="s">
+        <v>308</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
         <v>67</v>
-      </c>
-      <c r="D8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" t="s">
-        <v>68</v>
       </c>
       <c r="G8">
         <v>18</v>
@@ -2248,42 +2220,39 @@
         <v>320</v>
       </c>
       <c r="Y8">
-        <v>4</v>
+        <v>482</v>
       </c>
       <c r="Z8">
-        <v>482</v>
+        <v>0.2</v>
       </c>
       <c r="AA8">
-        <v>0.2</v>
+        <v>0.95</v>
       </c>
       <c r="AB8">
         <v>0.95</v>
       </c>
       <c r="AC8">
-        <v>0.95</v>
-      </c>
-      <c r="AD8">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s">
+        <v>308</v>
+      </c>
+      <c r="E9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" t="s">
         <v>67</v>
-      </c>
-      <c r="D9" t="s">
-        <v>309</v>
-      </c>
-      <c r="E9" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" t="s">
-        <v>68</v>
       </c>
       <c r="G9">
         <v>18</v>
@@ -2340,42 +2309,39 @@
         <v>320</v>
       </c>
       <c r="Y9">
-        <v>4</v>
+        <v>482</v>
       </c>
       <c r="Z9">
-        <v>482</v>
+        <v>0.2</v>
       </c>
       <c r="AA9">
-        <v>0.2</v>
+        <v>0.95</v>
       </c>
       <c r="AB9">
         <v>0.95</v>
       </c>
       <c r="AC9">
-        <v>0.95</v>
-      </c>
-      <c r="AD9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" t="s">
+        <v>308</v>
+      </c>
+      <c r="E10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" t="s">
         <v>67</v>
-      </c>
-      <c r="D10" t="s">
-        <v>319</v>
-      </c>
-      <c r="E10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" t="s">
-        <v>68</v>
       </c>
       <c r="G10">
         <v>18</v>
@@ -2457,51 +2423,51 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC93900-5A86-4519-AB89-460E8AC441EE}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.85546875" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="H1" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="I1" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>314</v>
-      </c>
       <c r="K1" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>3</v>
       </c>
@@ -2509,43 +2475,42 @@
         <v>4</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K2" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>1</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C3" s="8">
-        <f>2*35722</f>
-        <v>71444</v>
+        <v>35722</v>
       </c>
       <c r="D3" s="14">
         <v>38221</v>
@@ -2560,7 +2525,7 @@
         <v>4389</v>
       </c>
       <c r="H3" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" s="15">
         <v>2</v>
@@ -2569,7 +2534,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="8">
-        <v>2400</v>
+        <v>1200</v>
       </c>
     </row>
   </sheetData>
@@ -2581,40 +2546,40 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5C58D2-31A1-4CA6-99E5-3102447D41CF}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>64</v>
-      </c>
       <c r="G1" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>3</v>
       </c>
@@ -2622,30 +2587,30 @@
         <v>4</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>30</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>30</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>1</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C3" s="8">
         <v>42071</v>
@@ -2663,7 +2628,7 @@
         <v>79000</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2677,17 +2642,17 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H236"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -2701,10 +2666,10 @@
         <v>6</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>7</v>
@@ -2713,7 +2678,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2739,18 +2704,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E3">
         <v>128.27751563095319</v>
@@ -2765,18 +2730,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E4">
         <v>108.6922200994026</v>
@@ -2791,18 +2756,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E5">
         <v>89.967497678179427</v>
@@ -2817,18 +2782,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E6">
         <v>201.97398577601049</v>
@@ -2843,18 +2808,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E7">
         <v>220.67667390277779</v>
@@ -2869,18 +2834,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E8">
         <v>209.72740314793489</v>
@@ -2895,18 +2860,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E9">
         <v>236.95752516031689</v>
@@ -2921,18 +2886,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E10">
         <v>227.48034389692171</v>
@@ -2947,18 +2912,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E11">
         <v>217.37222962876629</v>
@@ -2973,18 +2938,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E12">
         <v>228.3347547488614</v>
@@ -2999,18 +2964,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E13">
         <v>198.64914670545039</v>
@@ -3025,18 +2990,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E14">
         <v>209.61881225684189</v>
@@ -3051,18 +3016,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E15">
         <v>179.92024457005471</v>
@@ -3077,18 +3042,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E16">
         <v>190.89572933352599</v>
@@ -3103,18 +3068,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E17">
         <v>160.33494903850419</v>
@@ -3129,18 +3094,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D18" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E18">
         <v>171.29747415859919</v>
@@ -3155,18 +3120,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D19" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E19">
         <v>141.61186611518809</v>
@@ -3181,18 +3146,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D20" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E20">
         <v>152.58153166657979</v>
@@ -3207,18 +3172,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E21">
         <v>122.88376366463569</v>
@@ -3233,18 +3198,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E22">
         <v>151.8291494252839</v>
@@ -3259,18 +3224,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E23">
         <v>171.42740460021071</v>
@@ -3285,18 +3250,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E24">
         <v>159.45191983673939</v>
@@ -3311,18 +3276,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D25" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E25">
         <v>190.15048752352669</v>
@@ -3337,18 +3302,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E26">
         <v>178.18082197213499</v>
@@ -3363,18 +3328,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E27">
         <v>208.86643001554609</v>
@@ -3389,18 +3354,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D28" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E28">
         <v>196.90390489545109</v>
@@ -3415,18 +3380,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E29">
         <v>228.46468519047289</v>
@@ -3441,18 +3406,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D30" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E30">
         <v>216.48920042700169</v>
@@ -3467,18 +3432,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D31" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E31">
         <v>241.37076070927091</v>
@@ -3493,18 +3458,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E32">
         <v>235.21810256239729</v>
@@ -3519,18 +3484,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D33" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E33">
         <v>222.6316481385478</v>
@@ -3545,18 +3510,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E34">
         <v>232.61734333734651</v>
@@ -3571,18 +3536,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D35" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E35">
         <v>204.04808558060819</v>
@@ -3597,18 +3562,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D36" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E36">
         <v>214.01671000373889</v>
@@ -3623,18 +3588,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C37" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D37" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E37">
         <v>185.32500265729209</v>
@@ -3649,18 +3614,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E38">
         <v>195.29466820868379</v>
@@ -3675,18 +3640,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E39">
         <v>166.59610052189649</v>
@@ -3701,18 +3666,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E40">
         <v>176.57158528536769</v>
@@ -3727,18 +3692,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E41">
         <v>147.01080499034589</v>
@@ -3753,18 +3718,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C42" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E42">
         <v>156.97333011044091</v>
@@ -3779,18 +3744,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C43" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D43" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E43">
         <v>128.2877220670299</v>
@@ -3805,18 +3770,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C44" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D44" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E44">
         <v>138.25738761842149</v>
@@ -3831,18 +3796,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C45" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D45" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E45">
         <v>109.5588199316343</v>
@@ -3857,18 +3822,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D46" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E46">
         <v>119.5343046951055</v>
@@ -3883,18 +3848,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C47" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D47" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E47">
         <v>89.969338245510826</v>
@@ -3909,18 +3874,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C48" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D48" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E48">
         <v>122.5211284864062</v>
@@ -3935,18 +3900,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C49" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D49" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E49">
         <v>111.5456437229349</v>
@@ -3961,18 +3926,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C50" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E50">
         <v>141.2442114097222</v>
@@ -3987,18 +3952,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C51" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D51" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E51">
         <v>130.27454585833061</v>
@@ -4013,18 +3978,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C52" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D52" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E52">
         <v>159.96015390174159</v>
@@ -4039,18 +4004,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C53" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D53" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E53">
         <v>148.9976287816466</v>
@@ -4065,18 +4030,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C54" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D54" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E54">
         <v>179.5584090766684</v>
@@ -4091,18 +4056,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C55" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D55" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E55">
         <v>168.5829243131972</v>
@@ -4117,18 +4082,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C56" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D56" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E56">
         <v>198.28149199998441</v>
@@ -4143,18 +4108,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C57" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D57" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E57">
         <v>187.3118264485928</v>
@@ -4169,18 +4134,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C58" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D58" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E58">
         <v>216.99743449200389</v>
@@ -4195,18 +4160,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C59" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D59" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E59">
         <v>206.03490937190881</v>
@@ -4221,18 +4186,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C60" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D60" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E60">
         <v>236.46072249545111</v>
@@ -4247,18 +4212,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C61" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D61" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E61">
         <v>225.62020490345941</v>
@@ -4273,18 +4238,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C62" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D62" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E62">
         <v>235.7639384322182</v>
@@ -4299,18 +4264,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C63" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D63" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E63">
         <v>243.42033131709979</v>
@@ -4325,18 +4290,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C64" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D64" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E64">
         <v>217.0350362968226</v>
@@ -4351,18 +4316,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C65" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D65" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E65">
         <v>228.0105210602938</v>
@@ -4377,18 +4342,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C66" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D66" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E66">
         <v>197.449740765272</v>
@@ -4403,18 +4368,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C67" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D67" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E67">
         <v>208.41226588536699</v>
@@ -4429,18 +4394,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C68" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D68" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E68">
         <v>178.7266578419559</v>
@@ -4455,18 +4420,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C69" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D69" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E69">
         <v>189.6963233933476</v>
@@ -4481,18 +4446,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C70" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D70" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E70">
         <v>159.9977557065603</v>
@@ -4507,18 +4472,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C71" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D71" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E71">
         <v>170.97324047003161</v>
@@ -4533,18 +4498,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C72" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D72" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E72">
         <v>140.4124601750097</v>
@@ -4559,18 +4524,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C73" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D73" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E73">
         <v>151.37498529510481</v>
@@ -4585,18 +4550,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C74" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D74" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E74">
         <v>121.6852931801608</v>
@@ -4611,18 +4576,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>73</v>
       </c>
       <c r="B75" t="s">
+        <v>144</v>
+      </c>
+      <c r="C75" t="s">
         <v>145</v>
       </c>
-      <c r="C75" t="s">
-        <v>146</v>
-      </c>
       <c r="D75" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E75">
         <v>123.885596888931</v>
@@ -4637,18 +4602,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C76" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D76" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E76">
         <v>153.5889205179574</v>
@@ -4663,18 +4628,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C77" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D77" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E77">
         <v>142.61925496656579</v>
@@ -4689,18 +4654,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D78" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E78">
         <v>172.30486300997691</v>
@@ -4715,18 +4680,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C79" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D79" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E79">
         <v>161.34233788988189</v>
@@ -4741,18 +4706,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C80" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D80" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E80">
         <v>191.905173849221</v>
@@ -4767,18 +4732,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C81" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D81" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E81">
         <v>180.92763342143249</v>
@@ -4793,18 +4758,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C82" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D82" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E82">
         <v>210.62620110821979</v>
@@ -4819,18 +4784,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C83" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D83" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E83">
         <v>199.65653555682809</v>
@@ -4845,18 +4810,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D84" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E84">
         <v>229.34214360023921</v>
@@ -4871,18 +4836,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C85" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D85" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E85">
         <v>218.37961848014419</v>
@@ -4897,18 +4862,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D86" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E86">
         <v>240.5122340430606</v>
@@ -4923,18 +4888,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C87" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D87" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E87">
         <v>237.96491401169479</v>
@@ -4949,18 +4914,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C88" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D88" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E88">
         <v>221.77312147233749</v>
@@ -4975,18 +4940,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C89" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D89" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E89">
         <v>232.7588166711362</v>
@@ -5001,18 +4966,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C90" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D90" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E90">
         <v>204.03890790919789</v>
@@ -5027,18 +4992,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C91" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D91" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E91">
         <v>215.02386676605781</v>
@@ -5053,18 +5018,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C92" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D92" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E92">
         <v>184.4536123776474</v>
@@ -5079,18 +5044,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C93" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D93" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E93">
         <v>195.4161374977424</v>
@@ -5105,18 +5070,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C94" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D94" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E94">
         <v>165.7305294543313</v>
@@ -5131,18 +5096,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C95" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D95" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E95">
         <v>176.70019500572289</v>
@@ -5157,18 +5122,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C96" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D96" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E96">
         <v>147.00162731893559</v>
@@ -5183,18 +5148,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C97" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D97" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E97">
         <v>157.9771120824069</v>
@@ -5209,18 +5174,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C98" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D98" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E98">
         <v>127.4163317873851</v>
@@ -5235,18 +5200,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C99" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D99" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E99">
         <v>138.3788569074801</v>
@@ -5261,18 +5226,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C100" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D100" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E100">
         <v>108.6932488640691</v>
@@ -5287,18 +5252,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C101" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D101" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E101">
         <v>119.6629144154607</v>
@@ -5313,18 +5278,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C102" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D102" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E102">
         <v>89.96608186922019</v>
@@ -5339,18 +5304,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>101</v>
       </c>
       <c r="B103" t="s">
+        <v>173</v>
+      </c>
+      <c r="C103" t="s">
         <v>174</v>
       </c>
-      <c r="C103" t="s">
-        <v>175</v>
-      </c>
       <c r="D103" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E103">
         <v>64.069064168333171</v>
@@ -5365,18 +5330,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C104" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D104" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E104">
         <v>93.754672211744264</v>
@@ -5391,18 +5356,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C105" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D105" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E105">
         <v>82.792147091649213</v>
@@ -5417,18 +5382,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C106" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D106" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E106">
         <v>113.352927386671</v>
@@ -5443,18 +5408,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D107" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E107">
         <v>102.3774426231998</v>
@@ -5469,18 +5434,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C108" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D108" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E108">
         <v>132.076010309987</v>
@@ -5495,18 +5460,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C109" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D109" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E109">
         <v>121.1063447585955</v>
@@ -5521,18 +5486,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C110" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D110" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E110">
         <v>150.79195280200651</v>
@@ -5547,18 +5512,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C111" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D111" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E111">
         <v>139.82942768191151</v>
@@ -5573,18 +5538,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C112" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D112" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E112">
         <v>170.39020797693331</v>
@@ -5599,18 +5564,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C113" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D113" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E113">
         <v>159.41472321346211</v>
@@ -5625,18 +5590,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C114" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D114" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E114">
         <v>189.11534656456661</v>
@@ -5651,18 +5616,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C115" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D115" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E115">
         <v>178.14362534885771</v>
@@ -5677,18 +5642,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C116" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D116" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E116">
         <v>207.8159790270166</v>
@@ -5703,18 +5668,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C117" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D117" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E117">
         <v>196.86670827217381</v>
@@ -5729,18 +5694,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C118" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D118" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E118">
         <v>226.43596602891211</v>
@@ -5755,18 +5720,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C119" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D119" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E119">
         <v>215.4654366187992</v>
@@ -5781,18 +5746,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C120" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D120" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E120">
         <v>216.52300416664019</v>
@@ -5807,18 +5772,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C121" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D121" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E121">
         <v>227.49266971803189</v>
@@ -5833,18 +5798,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C122" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D122" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E122">
         <v>197.79410203124459</v>
@@ -5859,18 +5824,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C123" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D123" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E123">
         <v>208.76958679471579</v>
@@ -5885,18 +5850,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C124" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D124" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E124">
         <v>178.20880649969399</v>
@@ -5911,18 +5876,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C125" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D125" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E125">
         <v>189.17133161978899</v>
@@ -5937,18 +5902,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C126" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D126" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E126">
         <v>159.48572357637801</v>
@@ -5963,18 +5928,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C127" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D127" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E127">
         <v>170.45538912776971</v>
@@ -5989,18 +5954,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C128" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D128" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E128">
         <v>140.76264065306199</v>
@@ -6015,18 +5980,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C129" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D129" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E129">
         <v>151.734361868771</v>
@@ -6041,18 +6006,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C130" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D130" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E130">
         <v>62.140495374628962</v>
@@ -6067,18 +6032,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C131" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D131" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E131">
         <v>91.71211573293472</v>
@@ -6093,18 +6058,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C132" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D132" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E132">
         <v>81.736630969463505</v>
@@ -6119,18 +6084,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C133" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D133" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E133">
         <v>110.4351986562508</v>
@@ -6145,18 +6110,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C134" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D134" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E134">
         <v>100.4655331048592</v>
@@ -6171,18 +6136,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C135" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D135" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E135">
         <v>129.15114114827031</v>
@@ -6197,18 +6162,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C136" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D136" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E136">
         <v>119.1886160281752</v>
@@ -6223,18 +6188,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C137" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D137" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E137">
         <v>148.749396323197</v>
@@ -6249,18 +6214,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C138" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D138" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E138">
         <v>138.7739115597258</v>
@@ -6275,18 +6240,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C139" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D139" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E139">
         <v>167.47247924651299</v>
@@ -6301,18 +6266,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C140" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D140" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E140">
         <v>157.5028136951214</v>
@@ -6327,18 +6292,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C141" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D141" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E141">
         <v>186.1884217385325</v>
@@ -6353,18 +6318,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C142" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D142" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E142">
         <v>176.2258966184375</v>
@@ -6379,18 +6344,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C143" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D143" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E143">
         <v>205.65170974197989</v>
@@ -6405,18 +6370,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C144" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D144" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E144">
         <v>195.8111921499881</v>
@@ -6431,18 +6396,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C145" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D145" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E145">
         <v>203.55997618212601</v>
@@ -6457,18 +6422,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C146" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D146" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E146">
         <v>213.61131856362849</v>
@@ -6483,18 +6448,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C147" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D147" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E147">
         <v>184.83107404673029</v>
@@ -6509,18 +6474,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C148" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D148" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E148">
         <v>196.80655881020161</v>
@@ -6535,18 +6500,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C149" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D149" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E149">
         <v>165.24577851517981</v>
@@ -6561,18 +6526,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C150" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D150" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E150">
         <v>177.2083036352748</v>
@@ -6587,18 +6552,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C151" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D151" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E151">
         <v>146.52269559186371</v>
@@ -6613,18 +6578,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C152" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D152" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E152">
         <v>158.49236114325541</v>
@@ -6639,18 +6604,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C153" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D153" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E153">
         <v>139.77133388425679</v>
@@ -6665,18 +6630,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>152</v>
       </c>
       <c r="B154" t="s">
+        <v>226</v>
+      </c>
+      <c r="C154" t="s">
         <v>227</v>
       </c>
-      <c r="C154" t="s">
-        <v>228</v>
-      </c>
       <c r="D154" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E154">
         <v>105.9528971832415</v>
@@ -6691,18 +6656,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C155" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D155" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E155">
         <v>95.977412419770289</v>
@@ -6717,18 +6682,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C156" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D156" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E156">
         <v>124.6759801065575</v>
@@ -6743,18 +6708,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C157" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D157" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E157">
         <v>114.7063145551659</v>
@@ -6769,18 +6734,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C158" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D158" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E158">
         <v>143.391922598577</v>
@@ -6795,18 +6760,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C159" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D159" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E159">
         <v>133.429397478482</v>
@@ -6821,18 +6786,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C160" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D160" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E160">
         <v>162.99017777350369</v>
@@ -6847,18 +6812,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C161" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D161" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E161">
         <v>153.01469301003249</v>
@@ -6873,18 +6838,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C162" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D162" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E162">
         <v>181.71326069681979</v>
@@ -6899,18 +6864,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C163" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D163" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E163">
         <v>171.7435951454282</v>
@@ -6925,18 +6890,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C164" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D164" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E164">
         <v>200.4292031888393</v>
@@ -6951,18 +6916,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C165" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D165" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E165">
         <v>190.46667806874419</v>
@@ -6977,18 +6942,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C166" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D166" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E166">
         <v>220.02745836376599</v>
@@ -7003,18 +6968,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C167" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D167" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E167">
         <v>210.0519736002949</v>
@@ -7029,18 +6994,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C168" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D168" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E168">
         <v>238.76583357246409</v>
@@ -7055,18 +7020,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C169" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D169" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E169">
         <v>228.7808757356905</v>
@@ -7081,18 +7046,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C170" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D170" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E170">
         <v>235.6082789584691</v>
@@ -7107,18 +7072,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C171" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D171" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E171">
         <v>246.51284726555139</v>
@@ -7133,18 +7098,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C172" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D172" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E172">
         <v>227.9855085470135</v>
@@ -7159,18 +7124,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C173" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D173" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E173">
         <v>209.2695660549941</v>
@@ -7185,18 +7150,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>172</v>
       </c>
       <c r="B174" t="s">
+        <v>247</v>
+      </c>
+      <c r="C174" t="s">
         <v>248</v>
       </c>
-      <c r="C174" t="s">
-        <v>249</v>
-      </c>
       <c r="D174" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E174">
         <v>150.851968632623</v>
@@ -7211,18 +7176,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C175" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D175" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E175">
         <v>139.87648386915191</v>
@@ -7237,18 +7202,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C176" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D176" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E176">
         <v>169.57505155593901</v>
@@ -7263,18 +7228,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C177" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D177" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E177">
         <v>158.60538600454751</v>
@@ -7289,18 +7254,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C178" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D178" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E178">
         <v>188.29099404795849</v>
@@ -7315,18 +7280,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C179" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D179" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E179">
         <v>177.3284689278635</v>
@@ -7341,18 +7306,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C180" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D180" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E180">
         <v>207.8892492228853</v>
@@ -7367,18 +7332,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C181" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D181" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E181">
         <v>196.9137644594141</v>
@@ -7393,18 +7358,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C182" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D182" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E182">
         <v>226.61233214620131</v>
@@ -7419,18 +7384,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C183" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D183" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E183">
         <v>215.64266659480981</v>
@@ -7445,18 +7410,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C184" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D184" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E184">
         <v>245.32827463822079</v>
@@ -7471,18 +7436,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C185" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D185" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E185">
         <v>234.3657495181258</v>
@@ -7497,18 +7462,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C186" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D186" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E186">
         <v>245.18216748396091</v>
@@ -7523,18 +7488,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D187" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E187">
         <v>253.9510450496764</v>
@@ -7549,18 +7514,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C188" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D188" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E188">
         <v>237.4287501120364</v>
@@ -7575,18 +7540,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C189" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D189" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E189">
         <v>219.70434205906821</v>
@@ -7601,18 +7566,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>188</v>
       </c>
       <c r="B190" t="s">
+        <v>264</v>
+      </c>
+      <c r="C190" t="s">
         <v>265</v>
       </c>
-      <c r="C190" t="s">
-        <v>266</v>
-      </c>
       <c r="D190" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E190">
         <v>113.0830304163233</v>
@@ -7627,18 +7592,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C191" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D191" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E191">
         <v>102.107545652852</v>
@@ -7653,18 +7618,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C192" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D192" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E192">
         <v>131.8061133396393</v>
@@ -7679,18 +7644,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C193" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D193" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E193">
         <v>120.8364477882477</v>
@@ -7705,18 +7670,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C194" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D194" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E194">
         <v>150.5220558316588</v>
@@ -7731,18 +7696,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C195" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D195" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E195">
         <v>139.55953071156381</v>
@@ -7757,18 +7722,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C196" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D196" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E196">
         <v>170.1203110065855</v>
@@ -7783,18 +7748,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C197" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D197" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E197">
         <v>159.14482624311441</v>
@@ -7809,18 +7774,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C198" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D198" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E198">
         <v>188.84339392990159</v>
@@ -7835,18 +7800,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C199" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D199" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E199">
         <v>177.87372837851001</v>
@@ -7861,18 +7826,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C200" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D200" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E200">
         <v>196.59681130182599</v>
@@ -7887,18 +7852,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C201" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D201" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E201">
         <v>216.18210683337671</v>
@@ -7913,18 +7878,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>200</v>
       </c>
       <c r="B202" t="s">
+        <v>277</v>
+      </c>
+      <c r="C202" t="s">
         <v>278</v>
       </c>
-      <c r="C202" t="s">
-        <v>279</v>
-      </c>
       <c r="D202" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E202">
         <v>121.4047543363185</v>
@@ -7939,18 +7904,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C203" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D203" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E203">
         <v>150.10332202310579</v>
@@ -7965,18 +7930,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C204" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D204" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E204">
         <v>140.1336564717142</v>
@@ -7991,18 +7956,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C205" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D205" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E205">
         <v>168.81926451512521</v>
@@ -8017,18 +7982,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C206" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D206" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E206">
         <v>158.85673939503019</v>
@@ -8043,18 +8008,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C207" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D207" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E207">
         <v>178.44203492658079</v>
@@ -8069,18 +8034,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C208" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D208" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E208">
         <v>197.1709370619765</v>
@@ -8095,18 +8060,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>207</v>
       </c>
       <c r="B209" t="s">
+        <v>285</v>
+      </c>
+      <c r="C209" t="s">
         <v>286</v>
       </c>
-      <c r="C209" t="s">
-        <v>287</v>
-      </c>
       <c r="D209" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E209">
         <v>113.4986155458283</v>
@@ -8121,18 +8086,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C210" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D210" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E210">
         <v>102.5289499944367</v>
@@ -8147,18 +8112,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C211" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D211" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E211">
         <v>121.2520329177527</v>
@@ -8173,18 +8138,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>210</v>
       </c>
       <c r="B212" t="s">
+        <v>289</v>
+      </c>
+      <c r="C212" t="s">
         <v>290</v>
       </c>
-      <c r="C212" t="s">
-        <v>291</v>
-      </c>
       <c r="D212" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E212">
         <v>107.16371920928221</v>
@@ -8199,90 +8164,90 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213"/>
       <c r="C213"/>
       <c r="D213"/>
       <c r="G213"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214"/>
       <c r="C214"/>
       <c r="D214"/>
       <c r="G214"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215"/>
       <c r="C215"/>
       <c r="D215"/>
       <c r="G215"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216"/>
       <c r="C216"/>
       <c r="D216"/>
       <c r="G216"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217"/>
       <c r="C217"/>
       <c r="D217"/>
       <c r="G217"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218"/>
       <c r="C218"/>
       <c r="D218"/>
       <c r="G218"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219"/>
       <c r="C219"/>
       <c r="D219"/>
       <c r="G219"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220"/>
       <c r="C220"/>
       <c r="D220"/>
       <c r="G220"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221"/>
       <c r="C221"/>
       <c r="D221"/>
       <c r="G221"/>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222"/>
       <c r="C222"/>
       <c r="D222"/>
       <c r="G222"/>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223"/>
       <c r="C223"/>
       <c r="D223"/>
       <c r="G223"/>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224"/>
       <c r="C224"/>
       <c r="D224"/>
       <c r="G224"/>
     </row>
-    <row r="225" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="226" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="227" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="228" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="229" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="230" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="231" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="232" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="233" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="234" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="235" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="236" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="225" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="226" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="227" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="228" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="229" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="230" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="231" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="232" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="233" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="234" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="235" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="236" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8295,14 +8260,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -8313,7 +8278,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -8324,111 +8289,111 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
